--- a/thread-strength/03_analyses/assemble-thread-summary/pad-area-worklist.xlsx
+++ b/thread-strength/03_analyses/assemble-thread-summary/pad-area-worklist.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t xml:space="preserve">mussel</t>
   </si>
@@ -45,204 +45,96 @@
     <t xml:space="preserve">picture</t>
   </si>
   <si>
-    <t xml:space="preserve">T021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baseline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pre</t>
+    <t xml:space="preserve">traces_pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">traces_post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">measured_pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">measured_post</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trace_paired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pair_usable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gap_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing_post_trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T013</t>
   </si>
   <si>
     <t xml:space="preserve">OA</t>
   </si>
   <si>
-    <t xml:space="preserve">00_baseline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T021_01.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/00_baseline/T021_01.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">available</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02_data/pictures/control/T21_01-02.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T021_02.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/00_baseline/T021_02.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T021_03.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/00_baseline/T021_03.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02_data/pictures/control/T21_03.png</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T134</t>
+    <t xml:space="preserve">T018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T137</t>
   </si>
   <si>
     <t xml:space="preserve">control</t>
   </si>
   <si>
-    <t xml:space="preserve">T134_02.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/00_baseline/T134_02.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">missing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T134_03.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/00_baseline/T134_03.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">treatment_control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01_treatment_control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T136_01.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/01_treatment_control/T136_01.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T136_02.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/01_treatment_control/T136_02.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T136_03.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/01_treatment_control/T136_03.jpg</t>
+    <t xml:space="preserve">T094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">missing_pre_trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T125</t>
   </si>
   <si>
     <t xml:space="preserve">T120</t>
   </si>
   <si>
-    <t xml:space="preserve">02_OA_treatment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T120_02.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/02_OA_treatment/T120_02.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T120_03.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03_analyses/extract-tensometer-data/QC_plots/02_OA_treatment/T120_03.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">traces_pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">traces_post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">measured_pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">measured_post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trace_paired</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pair_usable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gap_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images_missing_side_pre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">images_missing_side_post</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">missing_post_trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">missing_pre_trace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T125</t>
-  </si>
-  <si>
     <t xml:space="preserve">T035</t>
   </si>
   <si>
@@ -271,9 +163,6 @@
   </si>
   <si>
     <t xml:space="preserve">T124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pair_blocked_unmeasured</t>
   </si>
 </sst>
 </file>
@@ -634,312 +523,6 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" t="s">
-        <v>39</v>
-      </c>
-      <c r="H9" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J11"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -959,39 +542,33 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F1" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="G1" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="H1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="I1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J1" t="s">
-        <v>54</v>
-      </c>
-      <c r="K1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
@@ -1012,21 +589,15 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -1047,21 +618,15 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>58</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -1082,21 +647,15 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>58</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>2</v>
@@ -1117,21 +676,15 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>58</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
@@ -1152,21 +705,15 @@
         <v>0</v>
       </c>
       <c r="I6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
@@ -1187,21 +734,15 @@
         <v>0</v>
       </c>
       <c r="I7" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
@@ -1222,21 +763,15 @@
         <v>0</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
@@ -1257,21 +792,15 @@
         <v>0</v>
       </c>
       <c r="I9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -1292,21 +821,15 @@
         <v>0</v>
       </c>
       <c r="I10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
@@ -1327,21 +850,15 @@
         <v>0</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
@@ -1362,21 +879,15 @@
         <v>0</v>
       </c>
       <c r="I12" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
@@ -1397,21 +908,15 @@
         <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
@@ -1432,21 +937,15 @@
         <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
@@ -1467,21 +966,15 @@
         <v>0</v>
       </c>
       <c r="I15" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1502,21 +995,15 @@
         <v>0</v>
       </c>
       <c r="I16" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1537,21 +1024,15 @@
         <v>0</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1563,7 +1044,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" t="b">
         <v>0</v>
@@ -1572,21 +1053,15 @@
         <v>0</v>
       </c>
       <c r="I18" t="s">
-        <v>74</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1607,21 +1082,15 @@
         <v>0</v>
       </c>
       <c r="I19" t="s">
-        <v>74</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -1642,21 +1111,15 @@
         <v>0</v>
       </c>
       <c r="I20" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1677,21 +1140,15 @@
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>74</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1712,21 +1169,15 @@
         <v>0</v>
       </c>
       <c r="I22" t="s">
-        <v>74</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
@@ -1747,21 +1198,15 @@
         <v>0</v>
       </c>
       <c r="I23" t="s">
-        <v>74</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1782,21 +1227,15 @@
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>74</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1817,21 +1256,15 @@
         <v>0</v>
       </c>
       <c r="I25" t="s">
-        <v>74</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1852,21 +1285,15 @@
         <v>0</v>
       </c>
       <c r="I26" t="s">
-        <v>74</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1887,21 +1314,15 @@
         <v>0</v>
       </c>
       <c r="I27" t="s">
-        <v>74</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1922,83 +1343,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="s">
-        <v>74</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" t="s">
-        <v>86</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" t="s">
-        <v>86</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
